--- a/SSIS-Project/Timesheets/Teolan/Teolan_Govender_March_FinalWeek.xlsx
+++ b/SSIS-Project/Timesheets/Teolan/Teolan_Govender_March_FinalWeek.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://northerndata-my.sharepoint.com/personal/teolan_govender_sambeconsulting_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sc_TeolanGovender_2026\SSIS-Project\Timesheets\Teolan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="815" documentId="8_{74F04D01-1551-4C55-86B2-A96DA851F196}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76E9F9BB-33FB-4FB5-AE37-BD084B3296C2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1F6956-4ACC-47F1-8286-450155F24F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
   </bookViews>
@@ -2126,13 +2126,28 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2148,21 +2163,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3441,10 +3441,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2E876225-7964-4082-91F1-C6221C464408}" name="WorkType" displayName="WorkType" ref="H2:H77" totalsRowShown="0" headerRowDxfId="102" dataDxfId="101">
   <autoFilter ref="H2:H77" xr:uid="{2E876225-7964-4082-91F1-C6221C464408}"/>
@@ -8231,7 +8227,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>107</v>
+        <v>228</v>
       </c>
       <c r="C5" s="37"/>
       <c r="H5" s="40"/>
@@ -13352,118 +13348,118 @@
       <c r="F7" s="86"/>
     </row>
     <row r="8" spans="1:15" ht="27.4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="126" t="s">
+      <c r="A8" s="123" t="s">
         <v>183</v>
       </c>
-      <c r="B8" s="126"/>
-      <c r="C8" s="126"/>
-      <c r="D8" s="126"/>
-      <c r="E8" s="126"/>
-      <c r="F8" s="126"/>
+      <c r="B8" s="123"/>
+      <c r="C8" s="123"/>
+      <c r="D8" s="123"/>
+      <c r="E8" s="123"/>
+      <c r="F8" s="123"/>
     </row>
     <row r="9" spans="1:15" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="83" t="s">
         <v>187</v>
       </c>
-      <c r="B9" s="129" t="s">
+      <c r="B9" s="120" t="s">
         <v>184</v>
       </c>
-      <c r="C9" s="130"/>
-      <c r="D9" s="129" t="s">
+      <c r="C9" s="121"/>
+      <c r="D9" s="120" t="s">
         <v>93</v>
       </c>
-      <c r="E9" s="130"/>
+      <c r="E9" s="121"/>
       <c r="F9" s="84" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A10" s="79"/>
-      <c r="B10" s="120" t="s">
+      <c r="B10" s="122" t="s">
         <v>185</v>
       </c>
-      <c r="C10" s="120"/>
-      <c r="D10" s="120" t="s">
+      <c r="C10" s="122"/>
+      <c r="D10" s="122" t="s">
         <v>130</v>
       </c>
-      <c r="E10" s="120"/>
+      <c r="E10" s="122"/>
       <c r="F10" s="78">
         <v>200</v>
       </c>
-      <c r="G10" s="127" t="s">
+      <c r="G10" s="118" t="s">
         <v>186</v>
       </c>
-      <c r="H10" s="128"/>
-      <c r="I10" s="128"/>
-      <c r="J10" s="128"/>
-      <c r="K10" s="128"/>
-      <c r="L10" s="128"/>
-      <c r="M10" s="128"/>
-      <c r="N10" s="128"/>
-      <c r="O10" s="128"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="119"/>
+      <c r="J10" s="119"/>
+      <c r="K10" s="119"/>
+      <c r="L10" s="119"/>
+      <c r="M10" s="119"/>
+      <c r="N10" s="119"/>
+      <c r="O10" s="119"/>
     </row>
     <row r="11" spans="1:15" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A11" s="79"/>
-      <c r="B11" s="118" t="s">
+      <c r="B11" s="124" t="s">
         <v>188</v>
       </c>
-      <c r="C11" s="119"/>
-      <c r="D11" s="120" t="s">
+      <c r="C11" s="125"/>
+      <c r="D11" s="122" t="s">
         <v>136</v>
       </c>
-      <c r="E11" s="120"/>
+      <c r="E11" s="122"/>
       <c r="F11" s="78"/>
     </row>
     <row r="12" spans="1:15" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A12" s="79"/>
-      <c r="B12" s="118" t="s">
+      <c r="B12" s="124" t="s">
         <v>189</v>
       </c>
-      <c r="C12" s="119"/>
-      <c r="D12" s="120"/>
-      <c r="E12" s="120"/>
+      <c r="C12" s="125"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="122"/>
       <c r="F12" s="78"/>
     </row>
     <row r="13" spans="1:15" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A13" s="79"/>
-      <c r="B13" s="118"/>
-      <c r="C13" s="119"/>
-      <c r="D13" s="120"/>
-      <c r="E13" s="120"/>
+      <c r="B13" s="124"/>
+      <c r="C13" s="125"/>
+      <c r="D13" s="122"/>
+      <c r="E13" s="122"/>
       <c r="F13" s="78"/>
     </row>
     <row r="14" spans="1:15" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A14" s="79"/>
-      <c r="B14" s="118"/>
-      <c r="C14" s="119"/>
-      <c r="D14" s="120"/>
-      <c r="E14" s="120"/>
+      <c r="B14" s="124"/>
+      <c r="C14" s="125"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
       <c r="F14" s="78"/>
     </row>
     <row r="15" spans="1:15" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A15" s="79"/>
-      <c r="B15" s="124"/>
-      <c r="C15" s="125"/>
-      <c r="D15" s="120"/>
-      <c r="E15" s="120"/>
+      <c r="B15" s="129"/>
+      <c r="C15" s="130"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="122"/>
       <c r="F15" s="78"/>
     </row>
     <row r="16" spans="1:15" ht="13.15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="79"/>
-      <c r="B16" s="118"/>
-      <c r="C16" s="119"/>
-      <c r="D16" s="120"/>
-      <c r="E16" s="120"/>
+      <c r="B16" s="124"/>
+      <c r="C16" s="125"/>
+      <c r="D16" s="122"/>
+      <c r="E16" s="122"/>
       <c r="F16" s="78"/>
     </row>
     <row r="17" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="121" t="s">
+      <c r="A17" s="126" t="s">
         <v>95</v>
       </c>
-      <c r="B17" s="122"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="122"/>
-      <c r="E17" s="123"/>
+      <c r="B17" s="127"/>
+      <c r="C17" s="127"/>
+      <c r="D17" s="127"/>
+      <c r="E17" s="128"/>
       <c r="F17" s="77">
         <f>SUM(F10:F16)</f>
         <v>200</v>
@@ -13479,16 +13475,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="G10:O10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="A17:E17"/>
@@ -13498,6 +13484,16 @@
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G10:O10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7 D18" xr:uid="{517DF1E8-3052-48CF-9AE1-C19E6ECB6686}">
@@ -14614,6 +14610,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -14622,22 +14624,39 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4F2C86D-6131-4266-84D3-BE8E7F63755D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4F2C86D-6131-4266-84D3-BE8E7F63755D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AC3B20F-3DA5-41E6-83ED-7E6C76D4B764}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65AD6DCD-C979-41C2-B150-658688DCE060}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65AD6DCD-C979-41C2-B150-658688DCE060}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AC3B20F-3DA5-41E6-83ED-7E6C76D4B764}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/SSIS-Project/Timesheets/Teolan/Teolan_Govender_March_FinalWeek.xlsx
+++ b/SSIS-Project/Timesheets/Teolan/Teolan_Govender_March_FinalWeek.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sc_TeolanGovender_2026\SSIS-Project\Timesheets\Teolan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1F6956-4ACC-47F1-8286-450155F24F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81FB146C-B9C2-4C3F-87CF-C610041DB79C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
   </bookViews>
@@ -736,9 +736,6 @@
     <t>Started working on dream boards</t>
   </si>
   <si>
-    <t>Met with Shaila, Angela and the team for first onboarding and Discovery registration meeting</t>
-  </si>
-  <si>
     <t>Continued working on dream boards</t>
   </si>
   <si>
@@ -1034,6 +1031,9 @@
   </si>
   <si>
     <t>Join retrospective meeting with Bongani</t>
+  </si>
+  <si>
+    <t>Met with Shaila, Angela and the team for first onboarding and Discovery registration meeting - update</t>
   </si>
 </sst>
 </file>
@@ -2126,28 +2126,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2163,6 +2148,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -8300,7 +8300,7 @@
       <c r="I9" s="35"/>
       <c r="J9" s="35"/>
     </row>
-    <row r="10" spans="1:10" ht="37.9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A10" s="22">
         <v>46083</v>
       </c>
@@ -8318,7 +8318,7 @@
         <v>15</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>231</v>
+        <v>330</v>
       </c>
       <c r="H10" s="29">
         <f t="shared" ref="H10:H159" si="0">J10-I10</f>
@@ -8380,7 +8380,7 @@
         <v>15</v>
       </c>
       <c r="G12" s="28" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H12" s="29">
         <f t="shared" si="0"/>
@@ -8411,7 +8411,7 @@
         <v>15</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H13" s="29">
         <f t="shared" si="0"/>
@@ -8442,7 +8442,7 @@
         <v>15</v>
       </c>
       <c r="G14" s="28" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H14" s="29">
         <f t="shared" si="0"/>
@@ -8473,7 +8473,7 @@
         <v>15</v>
       </c>
       <c r="G15" s="28" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H15" s="29">
         <f t="shared" si="0"/>
@@ -8504,7 +8504,7 @@
         <v>15</v>
       </c>
       <c r="G16" s="28" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H16" s="29">
         <f t="shared" si="0"/>
@@ -8535,7 +8535,7 @@
         <v>15</v>
       </c>
       <c r="G17" s="28" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H17" s="29">
         <f t="shared" si="0"/>
@@ -8566,7 +8566,7 @@
         <v>15</v>
       </c>
       <c r="G18" s="28" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H18" s="29">
         <f t="shared" si="0"/>
@@ -8597,7 +8597,7 @@
         <v>15</v>
       </c>
       <c r="G19" s="28" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H19" s="29">
         <f t="shared" si="0"/>
@@ -8628,7 +8628,7 @@
         <v>15</v>
       </c>
       <c r="G20" s="28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H20" s="29">
         <f t="shared" si="0"/>
@@ -8659,7 +8659,7 @@
         <v>15</v>
       </c>
       <c r="G21" s="28" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H21" s="29">
         <f t="shared" si="0"/>
@@ -8690,7 +8690,7 @@
         <v>15</v>
       </c>
       <c r="G22" s="28" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H22" s="29">
         <f t="shared" si="0"/>
@@ -8721,7 +8721,7 @@
         <v>15</v>
       </c>
       <c r="G23" s="28" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H23" s="29">
         <f t="shared" si="0"/>
@@ -8752,7 +8752,7 @@
         <v>15</v>
       </c>
       <c r="G24" s="28" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H24" s="29">
         <f t="shared" si="0"/>
@@ -8783,7 +8783,7 @@
         <v>15</v>
       </c>
       <c r="G25" s="28" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H25" s="29">
         <f t="shared" si="0"/>
@@ -8814,7 +8814,7 @@
         <v>15</v>
       </c>
       <c r="G26" s="28" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H26" s="29">
         <f t="shared" si="0"/>
@@ -8845,7 +8845,7 @@
         <v>15</v>
       </c>
       <c r="G27" s="28" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H27" s="29">
         <f t="shared" si="0"/>
@@ -8858,7 +8858,7 @@
         <v>0.34027777777777779</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="22">
         <v>46087</v>
       </c>
@@ -8876,7 +8876,7 @@
         <v>15</v>
       </c>
       <c r="G28" s="28" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H28" s="29">
         <f t="shared" si="0"/>
@@ -8889,7 +8889,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A29" s="22">
         <v>46087</v>
       </c>
@@ -8907,7 +8907,7 @@
         <v>15</v>
       </c>
       <c r="G29" s="28" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H29" s="29">
         <f t="shared" si="0"/>
@@ -8920,7 +8920,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="37.9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A30" s="22">
         <v>46087</v>
       </c>
@@ -8938,7 +8938,7 @@
         <v>15</v>
       </c>
       <c r="G30" s="28" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H30" s="29">
         <f t="shared" si="0"/>
@@ -8951,7 +8951,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="31">
         <v>46088</v>
       </c>
@@ -8970,7 +8970,7 @@
       <c r="I31" s="35"/>
       <c r="J31" s="35"/>
     </row>
-    <row r="32" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="31">
         <v>46089</v>
       </c>
@@ -8989,7 +8989,7 @@
       <c r="I32" s="35"/>
       <c r="J32" s="35"/>
     </row>
-    <row r="33" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A33" s="22">
         <v>46090</v>
       </c>
@@ -9007,7 +9007,7 @@
         <v>15</v>
       </c>
       <c r="G33" s="28" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H33" s="29">
         <f t="shared" si="0"/>
@@ -9020,7 +9020,7 @@
         <v>0.34027777777777779</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A34" s="22">
         <v>46090</v>
       </c>
@@ -9038,7 +9038,7 @@
         <v>15</v>
       </c>
       <c r="G34" s="28" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H34" s="29">
         <f t="shared" si="0"/>
@@ -9051,7 +9051,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A35" s="22">
         <v>46090</v>
       </c>
@@ -9069,7 +9069,7 @@
         <v>15</v>
       </c>
       <c r="G35" s="28" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H35" s="29">
         <f t="shared" si="0"/>
@@ -9082,7 +9082,7 @@
         <v>0.45277777777777778</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" s="22">
         <v>46090</v>
       </c>
@@ -9100,7 +9100,7 @@
         <v>15</v>
       </c>
       <c r="G36" s="28" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H36" s="29">
         <f t="shared" si="0"/>
@@ -9113,7 +9113,7 @@
         <v>0.50694444444444442</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A37" s="22">
         <v>46090</v>
       </c>
@@ -9131,7 +9131,7 @@
         <v>15</v>
       </c>
       <c r="G37" s="28" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H37" s="29">
         <f t="shared" si="0"/>
@@ -9144,7 +9144,7 @@
         <v>0.60416666666666663</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A38" s="22">
         <v>46090</v>
       </c>
@@ -9162,7 +9162,7 @@
         <v>15</v>
       </c>
       <c r="G38" s="28" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H38" s="29">
         <f t="shared" si="0"/>
@@ -9175,7 +9175,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A39" s="22">
         <v>46090</v>
       </c>
@@ -9193,7 +9193,7 @@
         <v>15</v>
       </c>
       <c r="G39" s="28" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H39" s="29">
         <f t="shared" si="0"/>
@@ -9206,7 +9206,7 @@
         <v>0.6875</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A40" s="22">
         <v>46090</v>
       </c>
@@ -9224,7 +9224,7 @@
         <v>15</v>
       </c>
       <c r="G40" s="28" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H40" s="29">
         <f t="shared" si="0"/>
@@ -9237,7 +9237,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="37.9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A41" s="22">
         <v>46091</v>
       </c>
@@ -9255,7 +9255,7 @@
         <v>15</v>
       </c>
       <c r="G41" s="28" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H41" s="29">
         <f t="shared" si="0"/>
@@ -9268,7 +9268,7 @@
         <v>0.34375</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="22">
         <v>46091</v>
       </c>
@@ -9286,7 +9286,7 @@
         <v>15</v>
       </c>
       <c r="G42" s="28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H42" s="29">
         <f t="shared" si="0"/>
@@ -9299,7 +9299,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="22">
         <v>46091</v>
       </c>
@@ -9317,7 +9317,7 @@
         <v>15</v>
       </c>
       <c r="G43" s="28" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H43" s="29">
         <f t="shared" si="0"/>
@@ -9330,7 +9330,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="22">
         <v>46091</v>
       </c>
@@ -9348,7 +9348,7 @@
         <v>15</v>
       </c>
       <c r="G44" s="28" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H44" s="29">
         <f t="shared" si="0"/>
@@ -9361,7 +9361,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A45" s="22">
         <v>46091</v>
       </c>
@@ -9379,7 +9379,7 @@
         <v>15</v>
       </c>
       <c r="G45" s="28" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H45" s="29">
         <f t="shared" si="0"/>
@@ -9392,7 +9392,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A46" s="22">
         <v>46092</v>
       </c>
@@ -9410,7 +9410,7 @@
         <v>15</v>
       </c>
       <c r="G46" s="28" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H46" s="29">
         <f t="shared" si="0"/>
@@ -9423,7 +9423,7 @@
         <v>0.34027777777777779</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="22">
         <v>46092</v>
       </c>
@@ -9441,7 +9441,7 @@
         <v>15</v>
       </c>
       <c r="G47" s="28" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H47" s="29">
         <f t="shared" si="0"/>
@@ -9454,7 +9454,7 @@
         <v>0.4548611111111111</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="37.9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A48" s="22">
         <v>46092</v>
       </c>
@@ -9472,7 +9472,7 @@
         <v>15</v>
       </c>
       <c r="G48" s="28" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H48" s="29">
         <f t="shared" si="0"/>
@@ -9485,7 +9485,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="22">
         <v>46092</v>
       </c>
@@ -9503,7 +9503,7 @@
         <v>15</v>
       </c>
       <c r="G49" s="28" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H49" s="29">
         <f t="shared" si="0"/>
@@ -9516,7 +9516,7 @@
         <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="22">
         <v>46092</v>
       </c>
@@ -9534,7 +9534,7 @@
         <v>15</v>
       </c>
       <c r="G50" s="28" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H50" s="29">
         <f t="shared" si="0"/>
@@ -9547,7 +9547,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="50.45" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A51" s="22">
         <v>46092</v>
       </c>
@@ -9565,7 +9565,7 @@
         <v>15</v>
       </c>
       <c r="G51" s="28" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H51" s="29">
         <f t="shared" si="0"/>
@@ -9578,7 +9578,7 @@
         <v>0.6875</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="22">
         <v>46092</v>
       </c>
@@ -9596,7 +9596,7 @@
         <v>15</v>
       </c>
       <c r="G52" s="28" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H52" s="29">
         <f t="shared" si="0"/>
@@ -9609,7 +9609,7 @@
         <v>0.72916666666666663</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A53" s="22">
         <v>46093</v>
       </c>
@@ -9627,7 +9627,7 @@
         <v>15</v>
       </c>
       <c r="G53" s="28" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H53" s="29">
         <f t="shared" si="0"/>
@@ -9640,7 +9640,7 @@
         <v>0.34375</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A54" s="22">
         <v>46093</v>
       </c>
@@ -9658,7 +9658,7 @@
         <v>15</v>
       </c>
       <c r="G54" s="28" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H54" s="29">
         <f t="shared" si="0"/>
@@ -9671,7 +9671,7 @@
         <v>0.3888888888888889</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A55" s="22">
         <v>46093</v>
       </c>
@@ -9689,7 +9689,7 @@
         <v>15</v>
       </c>
       <c r="G55" s="28" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H55" s="29">
         <f t="shared" si="0"/>
@@ -9702,7 +9702,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="37.9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A56" s="22">
         <v>46093</v>
       </c>
@@ -9720,7 +9720,7 @@
         <v>15</v>
       </c>
       <c r="G56" s="28" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H56" s="29">
         <f t="shared" si="0"/>
@@ -9733,7 +9733,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" s="22">
         <v>46093</v>
       </c>
@@ -9751,7 +9751,7 @@
         <v>15</v>
       </c>
       <c r="G57" s="28" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H57" s="29">
         <f t="shared" si="0"/>
@@ -9764,7 +9764,7 @@
         <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A58" s="22">
         <v>46093</v>
       </c>
@@ -9782,7 +9782,7 @@
         <v>15</v>
       </c>
       <c r="G58" s="28" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H58" s="29">
         <f t="shared" si="0"/>
@@ -9795,7 +9795,7 @@
         <v>0.60763888888888884</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" s="22">
         <v>46093</v>
       </c>
@@ -9813,7 +9813,7 @@
         <v>15</v>
       </c>
       <c r="G59" s="28" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H59" s="29">
         <f t="shared" si="0"/>
@@ -9826,7 +9826,7 @@
         <v>0.63194444444444442</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A60" s="22">
         <v>46093</v>
       </c>
@@ -9844,7 +9844,7 @@
         <v>15</v>
       </c>
       <c r="G60" s="28" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H60" s="29">
         <f t="shared" si="0"/>
@@ -9857,7 +9857,7 @@
         <v>0.65625</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="37.9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A61" s="22">
         <v>46093</v>
       </c>
@@ -9875,7 +9875,7 @@
         <v>15</v>
       </c>
       <c r="G61" s="28" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H61" s="29">
         <f t="shared" si="0"/>
@@ -9888,7 +9888,7 @@
         <v>0.6875</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" s="22">
         <v>46093</v>
       </c>
@@ -9906,7 +9906,7 @@
         <v>15</v>
       </c>
       <c r="G62" s="28" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H62" s="29">
         <f t="shared" si="0"/>
@@ -9919,7 +9919,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" s="22">
         <v>46094</v>
       </c>
@@ -9937,7 +9937,7 @@
         <v>15</v>
       </c>
       <c r="G63" s="28" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H63" s="29">
         <f t="shared" si="0"/>
@@ -9950,7 +9950,7 @@
         <v>0.35416666666666669</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" s="22">
         <v>46094</v>
       </c>
@@ -9968,7 +9968,7 @@
         <v>15</v>
       </c>
       <c r="G64" s="28" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H64" s="29">
         <f t="shared" si="0"/>
@@ -9981,7 +9981,7 @@
         <v>0.3888888888888889</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A65" s="22">
         <v>46094</v>
       </c>
@@ -9999,7 +9999,7 @@
         <v>15</v>
       </c>
       <c r="G65" s="28" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H65" s="29">
         <f t="shared" si="0"/>
@@ -10012,7 +10012,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A66" s="22">
         <v>46094</v>
       </c>
@@ -10030,7 +10030,7 @@
         <v>15</v>
       </c>
       <c r="G66" s="28" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H66" s="29">
         <f t="shared" si="0"/>
@@ -10043,7 +10043,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="37.9" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A67" s="22">
         <v>46094</v>
       </c>
@@ -10061,7 +10061,7 @@
         <v>15</v>
       </c>
       <c r="G67" s="28" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H67" s="29">
         <f t="shared" si="0"/>
@@ -10074,7 +10074,7 @@
         <v>0.52083333333333337</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A68" s="22">
         <v>46094</v>
       </c>
@@ -10092,7 +10092,7 @@
         <v>15</v>
       </c>
       <c r="G68" s="28" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H68" s="29">
         <f t="shared" si="0"/>
@@ -10105,7 +10105,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A69" s="22">
         <v>46094</v>
       </c>
@@ -10123,7 +10123,7 @@
         <v>15</v>
       </c>
       <c r="G69" s="28" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H69" s="29">
         <f t="shared" si="0"/>
@@ -10136,7 +10136,7 @@
         <v>0.6875</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" s="22">
         <v>46094</v>
       </c>
@@ -10154,7 +10154,7 @@
         <v>15</v>
       </c>
       <c r="G70" s="28" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H70" s="29">
         <f t="shared" si="0"/>
@@ -10167,7 +10167,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" s="31">
         <v>46095</v>
       </c>
@@ -10186,7 +10186,7 @@
       <c r="I71" s="35"/>
       <c r="J71" s="35"/>
     </row>
-    <row r="72" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" s="31">
         <v>46096</v>
       </c>
@@ -10205,7 +10205,7 @@
       <c r="I72" s="35"/>
       <c r="J72" s="35"/>
     </row>
-    <row r="73" spans="1:10" ht="50.45" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A73" s="22">
         <v>46097</v>
       </c>
@@ -10223,7 +10223,7 @@
         <v>15</v>
       </c>
       <c r="G73" s="28" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H73" s="29">
         <f t="shared" si="0"/>
@@ -10236,7 +10236,7 @@
         <v>0.37291666666666667</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A74" s="22">
         <v>46097</v>
       </c>
@@ -10254,7 +10254,7 @@
         <v>15</v>
       </c>
       <c r="G74" s="28" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H74" s="29">
         <f t="shared" si="0"/>
@@ -10267,7 +10267,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="37.9" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A75" s="22">
         <v>46097</v>
       </c>
@@ -10285,7 +10285,7 @@
         <v>15</v>
       </c>
       <c r="G75" s="28" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H75" s="29">
         <f t="shared" si="0"/>
@@ -10298,7 +10298,7 @@
         <v>0.51041666666666663</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A76" s="22">
         <v>46097</v>
       </c>
@@ -10316,7 +10316,7 @@
         <v>15</v>
       </c>
       <c r="G76" s="28" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H76" s="29">
         <f t="shared" si="0"/>
@@ -10329,7 +10329,7 @@
         <v>0.52083333333333337</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A77" s="22">
         <v>46097</v>
       </c>
@@ -10347,7 +10347,7 @@
         <v>15</v>
       </c>
       <c r="G77" s="28" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H77" s="29">
         <f t="shared" si="0"/>
@@ -10360,7 +10360,7 @@
         <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A78" s="22">
         <v>46097</v>
       </c>
@@ -10378,7 +10378,7 @@
         <v>15</v>
       </c>
       <c r="G78" s="28" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H78" s="29">
         <f t="shared" si="0"/>
@@ -10391,7 +10391,7 @@
         <v>0.60416666666666663</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A79" s="22">
         <v>46097</v>
       </c>
@@ -10409,7 +10409,7 @@
         <v>15</v>
       </c>
       <c r="G79" s="28" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H79" s="29">
         <f t="shared" si="0"/>
@@ -10422,7 +10422,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A80" s="22">
         <v>46097</v>
       </c>
@@ -10440,7 +10440,7 @@
         <v>15</v>
       </c>
       <c r="G80" s="28" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H80" s="29">
         <f t="shared" si="0"/>
@@ -10453,7 +10453,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" s="22">
         <v>46098</v>
       </c>
@@ -10471,7 +10471,7 @@
         <v>15</v>
       </c>
       <c r="G81" s="28" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H81" s="29">
         <f t="shared" si="0"/>
@@ -10484,7 +10484,7 @@
         <v>0.36805555555555558</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="37.9" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:10" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A82" s="22">
         <v>46098</v>
       </c>
@@ -10502,7 +10502,7 @@
         <v>15</v>
       </c>
       <c r="G82" s="28" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H82" s="29">
         <f t="shared" si="0"/>
@@ -10515,7 +10515,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" s="22">
         <v>46098</v>
       </c>
@@ -10533,7 +10533,7 @@
         <v>15</v>
       </c>
       <c r="G83" s="28" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H83" s="29">
         <f t="shared" si="0"/>
@@ -10546,7 +10546,7 @@
         <v>0.51458333333333328</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" s="22">
         <v>46098</v>
       </c>
@@ -10564,7 +10564,7 @@
         <v>15</v>
       </c>
       <c r="G84" s="28" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H84" s="29">
         <f t="shared" si="0"/>
@@ -10577,7 +10577,7 @@
         <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A85" s="22">
         <v>46098</v>
       </c>
@@ -10595,7 +10595,7 @@
         <v>15</v>
       </c>
       <c r="G85" s="28" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H85" s="29">
         <f t="shared" si="0"/>
@@ -10608,7 +10608,7 @@
         <v>0.60416666666666663</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" s="22">
         <v>46098</v>
       </c>
@@ -10626,7 +10626,7 @@
         <v>15</v>
       </c>
       <c r="G86" s="28" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H86" s="29">
         <f t="shared" si="0"/>
@@ -10639,7 +10639,7 @@
         <v>0.65625</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="37.9" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A87" s="22">
         <v>46098</v>
       </c>
@@ -10657,7 +10657,7 @@
         <v>15</v>
       </c>
       <c r="G87" s="28" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H87" s="29">
         <f t="shared" si="0"/>
@@ -10670,7 +10670,7 @@
         <v>0.73958333333333337</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" s="22">
         <v>46099</v>
       </c>
@@ -10688,7 +10688,7 @@
         <v>15</v>
       </c>
       <c r="G88" s="28" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H88" s="29">
         <f t="shared" si="0"/>
@@ -10701,7 +10701,7 @@
         <v>0.3611111111111111</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" s="22">
         <v>46099</v>
       </c>
@@ -10719,7 +10719,7 @@
         <v>15</v>
       </c>
       <c r="G89" s="28" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H89" s="29">
         <f t="shared" si="0"/>
@@ -10732,7 +10732,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" s="22">
         <v>46099</v>
       </c>
@@ -10750,7 +10750,7 @@
         <v>15</v>
       </c>
       <c r="G90" s="28" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H90" s="29">
         <f t="shared" si="0"/>
@@ -10763,7 +10763,7 @@
         <v>0.48958333333333331</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" s="22">
         <v>46099</v>
       </c>
@@ -10781,7 +10781,7 @@
         <v>15</v>
       </c>
       <c r="G91" s="28" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H91" s="29">
         <f t="shared" si="0"/>
@@ -10794,7 +10794,7 @@
         <v>0.52083333333333337</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92" s="22">
         <v>46099</v>
       </c>
@@ -10812,7 +10812,7 @@
         <v>15</v>
       </c>
       <c r="G92" s="28" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H92" s="29">
         <f t="shared" si="0"/>
@@ -10825,7 +10825,7 @@
         <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A93" s="22">
         <v>46099</v>
       </c>
@@ -10843,7 +10843,7 @@
         <v>15</v>
       </c>
       <c r="G93" s="28" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H93" s="29">
         <f t="shared" si="0"/>
@@ -10856,7 +10856,7 @@
         <v>0.60416666666666663</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94" s="22"/>
       <c r="B94" s="22"/>
       <c r="C94" s="27"/>
@@ -10868,7 +10868,7 @@
         <v>15</v>
       </c>
       <c r="G94" s="28" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H94" s="29">
         <f t="shared" si="0"/>
@@ -10881,7 +10881,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A95" s="22">
         <v>46099</v>
       </c>
@@ -10899,7 +10899,7 @@
         <v>15</v>
       </c>
       <c r="G95" s="28" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H95" s="29">
         <f t="shared" si="0"/>
@@ -10912,7 +10912,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A96" s="22">
         <v>46100</v>
       </c>
@@ -10930,7 +10930,7 @@
         <v>15</v>
       </c>
       <c r="G96" s="28" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H96" s="29">
         <f t="shared" si="0"/>
@@ -10943,7 +10943,7 @@
         <v>0.34722222222222221</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A97" s="22">
         <v>46100</v>
       </c>
@@ -10961,7 +10961,7 @@
         <v>15</v>
       </c>
       <c r="G97" s="28" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H97" s="29">
         <f t="shared" si="0"/>
@@ -10974,7 +10974,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A98" s="22">
         <v>46100</v>
       </c>
@@ -10992,7 +10992,7 @@
         <v>15</v>
       </c>
       <c r="G98" s="28" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H98" s="29">
         <f t="shared" si="0"/>
@@ -11005,7 +11005,7 @@
         <v>0.51388888888888884</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" s="22">
         <v>46100</v>
       </c>
@@ -11023,7 +11023,7 @@
         <v>15</v>
       </c>
       <c r="G99" s="28" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H99" s="29">
         <f t="shared" si="0"/>
@@ -11036,7 +11036,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A100" s="22">
         <v>46100</v>
       </c>
@@ -11054,7 +11054,7 @@
         <v>15</v>
       </c>
       <c r="G100" s="28" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H100" s="29">
         <f t="shared" si="0"/>
@@ -11067,7 +11067,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101" s="22">
         <v>46101</v>
       </c>
@@ -11085,7 +11085,7 @@
         <v>15</v>
       </c>
       <c r="G101" s="28" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H101" s="29">
         <f t="shared" si="0"/>
@@ -11098,7 +11098,7 @@
         <v>0.34166666666666667</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A102" s="22">
         <v>46101</v>
       </c>
@@ -11116,7 +11116,7 @@
         <v>15</v>
       </c>
       <c r="G102" s="28" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H102" s="29">
         <f t="shared" si="0"/>
@@ -11129,7 +11129,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A103" s="22">
         <v>46101</v>
       </c>
@@ -11147,7 +11147,7 @@
         <v>15</v>
       </c>
       <c r="G103" s="28" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H103" s="29">
         <f t="shared" si="0"/>
@@ -11160,7 +11160,7 @@
         <v>0.48958333333333331</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A104" s="22">
         <v>46101</v>
       </c>
@@ -11178,7 +11178,7 @@
         <v>15</v>
       </c>
       <c r="G104" s="28" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H104" s="29">
         <f t="shared" si="0"/>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="L104" s="64"/>
     </row>
-    <row r="105" spans="1:12" ht="37.9" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A105" s="22">
         <v>46101</v>
       </c>
@@ -11210,7 +11210,7 @@
         <v>15</v>
       </c>
       <c r="G105" s="28" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H105" s="29">
         <f t="shared" si="0"/>
@@ -11223,7 +11223,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A106" s="22">
         <v>46101</v>
       </c>
@@ -11241,7 +11241,7 @@
         <v>15</v>
       </c>
       <c r="G106" s="28" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H106" s="29">
         <f t="shared" si="0"/>
@@ -11254,7 +11254,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A107" s="22">
         <v>46101</v>
       </c>
@@ -11272,7 +11272,7 @@
         <v>15</v>
       </c>
       <c r="G107" s="28" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H107" s="29">
         <f>J107-I106</f>
@@ -11285,7 +11285,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" s="31">
         <v>46102</v>
       </c>
@@ -11316,7 +11316,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A109" s="31">
         <v>46103</v>
       </c>
@@ -11335,7 +11335,7 @@
       <c r="I109" s="35"/>
       <c r="J109" s="35"/>
     </row>
-    <row r="110" spans="1:12" ht="37.9" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A110" s="22">
         <v>46104</v>
       </c>
@@ -11353,7 +11353,7 @@
         <v>15</v>
       </c>
       <c r="G110" s="28" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H110" s="29">
         <f t="shared" si="0"/>
@@ -11366,7 +11366,7 @@
         <v>0.36458333333333331</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A111" s="22">
         <v>46104</v>
       </c>
@@ -11384,7 +11384,7 @@
         <v>15</v>
       </c>
       <c r="G111" s="28" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H111" s="29">
         <f t="shared" si="0"/>
@@ -11397,7 +11397,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A112" s="22">
         <v>46104</v>
       </c>
@@ -11415,7 +11415,7 @@
         <v>15</v>
       </c>
       <c r="G112" s="28" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H112" s="29">
         <f t="shared" si="0"/>
@@ -11428,7 +11428,7 @@
         <v>0.48958333333333331</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A113" s="22">
         <v>46104</v>
       </c>
@@ -11446,7 +11446,7 @@
         <v>15</v>
       </c>
       <c r="G113" s="28" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H113" s="29">
         <f t="shared" si="0"/>
@@ -11459,7 +11459,7 @@
         <v>0.52083333333333337</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A114" s="22">
         <v>46104</v>
       </c>
@@ -11477,7 +11477,7 @@
         <v>15</v>
       </c>
       <c r="G114" s="28" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H114" s="29">
         <f t="shared" si="0"/>
@@ -11490,7 +11490,7 @@
         <v>0.60416666666666663</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A115" s="22">
         <v>46104</v>
       </c>
@@ -11508,7 +11508,7 @@
         <v>15</v>
       </c>
       <c r="G115" s="28" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H115" s="29">
         <f t="shared" si="0"/>
@@ -11521,7 +11521,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A116" s="22">
         <v>46104</v>
       </c>
@@ -11539,7 +11539,7 @@
         <v>15</v>
       </c>
       <c r="G116" s="28" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H116" s="29">
         <f t="shared" si="0"/>
@@ -11552,7 +11552,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A117" s="22">
         <v>46104</v>
       </c>
@@ -11570,7 +11570,7 @@
         <v>15</v>
       </c>
       <c r="G117" s="28" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H117" s="29">
         <f t="shared" si="0"/>
@@ -11583,7 +11583,7 @@
         <v>0.6875</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A118" s="22">
         <v>46104</v>
       </c>
@@ -11601,7 +11601,7 @@
         <v>15</v>
       </c>
       <c r="G118" s="28" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H118" s="29">
         <f t="shared" si="0"/>
@@ -11614,7 +11614,7 @@
         <v>0.72916666666666663</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="37.9" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A119" s="22">
         <v>46105</v>
       </c>
@@ -11632,7 +11632,7 @@
         <v>15</v>
       </c>
       <c r="G119" s="28" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H119" s="29">
         <f t="shared" si="0"/>
@@ -11645,7 +11645,7 @@
         <v>0.39583333333333331</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A120" s="22">
         <v>46105</v>
       </c>
@@ -11663,7 +11663,7 @@
         <v>15</v>
       </c>
       <c r="G120" s="28" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H120" s="29">
         <f t="shared" si="0"/>
@@ -11676,7 +11676,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A121" s="22">
         <v>46105</v>
       </c>
@@ -11694,7 +11694,7 @@
         <v>15</v>
       </c>
       <c r="G121" s="28" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H121" s="29">
         <f t="shared" si="0"/>
@@ -11707,7 +11707,7 @@
         <v>0.51388888888888884</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A122" s="22">
         <v>46105</v>
       </c>
@@ -11725,7 +11725,7 @@
         <v>15</v>
       </c>
       <c r="G122" s="28" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H122" s="29">
         <f t="shared" si="0"/>
@@ -11738,7 +11738,7 @@
         <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="37.9" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A123" s="22">
         <v>46105</v>
       </c>
@@ -11756,7 +11756,7 @@
         <v>15</v>
       </c>
       <c r="G123" s="28" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H123" s="29">
         <f t="shared" si="0"/>
@@ -11769,7 +11769,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A124" s="22">
         <v>46105</v>
       </c>
@@ -11787,7 +11787,7 @@
         <v>15</v>
       </c>
       <c r="G124" s="28" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H124" s="29">
         <f t="shared" si="0"/>
@@ -11800,7 +11800,7 @@
         <v>0.6875</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A125" s="22">
         <v>46105</v>
       </c>
@@ -11818,7 +11818,7 @@
         <v>15</v>
       </c>
       <c r="G125" s="28" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H125" s="29">
         <f t="shared" si="0"/>
@@ -11831,7 +11831,7 @@
         <v>0.71875</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A126" s="22">
         <v>46106</v>
       </c>
@@ -11849,7 +11849,7 @@
         <v>15</v>
       </c>
       <c r="G126" s="28" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H126" s="29">
         <f t="shared" si="0"/>
@@ -11862,7 +11862,7 @@
         <v>0.34027777777777779</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A127" s="22">
         <v>46106</v>
       </c>
@@ -11880,7 +11880,7 @@
         <v>15</v>
       </c>
       <c r="G127" s="28" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H127" s="29">
         <f t="shared" si="0"/>
@@ -11893,7 +11893,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A128" s="22">
         <v>46106</v>
       </c>
@@ -11911,7 +11911,7 @@
         <v>15</v>
       </c>
       <c r="G128" s="28" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H128" s="29">
         <f t="shared" si="0"/>
@@ -11924,7 +11924,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A129" s="22">
         <v>46106</v>
       </c>
@@ -11942,7 +11942,7 @@
         <v>15</v>
       </c>
       <c r="G129" s="28" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H129" s="29">
         <f t="shared" si="0"/>
@@ -11955,7 +11955,7 @@
         <v>0.52083333333333337</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A130" s="22">
         <v>46106</v>
       </c>
@@ -11973,7 +11973,7 @@
         <v>15</v>
       </c>
       <c r="G130" s="28" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H130" s="29">
         <f t="shared" si="0"/>
@@ -11986,7 +11986,7 @@
         <v>0.60416666666666663</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A131" s="22">
         <v>46106</v>
       </c>
@@ -12004,7 +12004,7 @@
         <v>15</v>
       </c>
       <c r="G131" s="28" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H131" s="29">
         <f t="shared" si="0"/>
@@ -12017,7 +12017,7 @@
         <v>0.63888888888888884</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="50.45" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A132" s="22">
         <v>46106</v>
       </c>
@@ -12035,7 +12035,7 @@
         <v>15</v>
       </c>
       <c r="G132" s="28" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H132" s="29">
         <f t="shared" si="0"/>
@@ -12048,7 +12048,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A133" s="22">
         <v>46107</v>
       </c>
@@ -12066,7 +12066,7 @@
         <v>15</v>
       </c>
       <c r="G133" s="28" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H133" s="29">
         <f t="shared" si="0"/>
@@ -12079,7 +12079,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A134" s="22">
         <v>46107</v>
       </c>
@@ -12097,7 +12097,7 @@
         <v>15</v>
       </c>
       <c r="G134" s="28" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H134" s="29">
         <f t="shared" si="0"/>
@@ -12110,7 +12110,7 @@
         <v>0.39583333333333331</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A135" s="22">
         <v>46107</v>
       </c>
@@ -12128,7 +12128,7 @@
         <v>15</v>
       </c>
       <c r="G135" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H135" s="29">
         <f t="shared" si="0"/>
@@ -12141,7 +12141,7 @@
         <v>0.40277777777777779</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A136" s="22">
         <v>46107</v>
       </c>
@@ -12159,7 +12159,7 @@
         <v>15</v>
       </c>
       <c r="G136" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H136" s="29">
         <f t="shared" si="0"/>
@@ -12172,7 +12172,7 @@
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A137" s="22">
         <v>46107</v>
       </c>
@@ -12190,7 +12190,7 @@
         <v>15</v>
       </c>
       <c r="G137" s="28" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H137" s="29">
         <f t="shared" si="0"/>
@@ -12203,7 +12203,7 @@
         <v>0.49305555555555558</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A138" s="22">
         <v>46107</v>
       </c>
@@ -12221,7 +12221,7 @@
         <v>15</v>
       </c>
       <c r="G138" s="28" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H138" s="29">
         <f t="shared" si="0"/>
@@ -12234,7 +12234,7 @@
         <v>0.52083333333333337</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A139" s="22">
         <v>46107</v>
       </c>
@@ -12252,7 +12252,7 @@
         <v>15</v>
       </c>
       <c r="G139" s="28" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H139" s="29">
         <f t="shared" si="0"/>
@@ -12265,7 +12265,7 @@
         <v>0.60416666666666663</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A140" s="22">
         <v>46107</v>
       </c>
@@ -12283,7 +12283,7 @@
         <v>15</v>
       </c>
       <c r="G140" s="28" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H140" s="29">
         <f t="shared" si="0"/>
@@ -12296,7 +12296,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A141" s="22">
         <v>46107</v>
       </c>
@@ -12314,7 +12314,7 @@
         <v>15</v>
       </c>
       <c r="G141" s="28" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H141" s="29">
         <f t="shared" si="0"/>
@@ -12327,7 +12327,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A142" s="22">
         <v>46108</v>
       </c>
@@ -12345,7 +12345,7 @@
         <v>15</v>
       </c>
       <c r="G142" s="28" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H142" s="29">
         <f t="shared" si="0"/>
@@ -12358,7 +12358,7 @@
         <v>0.34722222222222221</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A143" s="22">
         <v>46108</v>
       </c>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="F143" s="27"/>
       <c r="G143" s="28" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H143" s="29">
         <f t="shared" si="0"/>
@@ -12387,7 +12387,7 @@
         <v>0.3611111111111111</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A144" s="22">
         <v>46108</v>
       </c>
@@ -12405,7 +12405,7 @@
         <v>15</v>
       </c>
       <c r="G144" s="28" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H144" s="29">
         <f t="shared" si="0"/>
@@ -12418,7 +12418,7 @@
         <v>0.40277777777777779</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A145" s="22">
         <v>46108</v>
       </c>
@@ -12436,7 +12436,7 @@
         <v>15</v>
       </c>
       <c r="G145" s="28" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H145" s="29">
         <f t="shared" si="0"/>
@@ -12449,7 +12449,7 @@
         <v>0.44791666666666669</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A146" s="22">
         <v>46108</v>
       </c>
@@ -12467,7 +12467,7 @@
         <v>15</v>
       </c>
       <c r="G146" s="28" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H146" s="29">
         <f t="shared" si="0"/>
@@ -12480,7 +12480,7 @@
         <v>0.48958333333333331</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A147" s="22">
         <v>46108</v>
       </c>
@@ -12498,7 +12498,7 @@
         <v>15</v>
       </c>
       <c r="G147" s="28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H147" s="29">
         <f t="shared" si="0"/>
@@ -12511,7 +12511,7 @@
         <v>0.52083333333333337</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A148" s="22">
         <v>46108</v>
       </c>
@@ -12529,7 +12529,7 @@
         <v>15</v>
       </c>
       <c r="G148" s="28" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H148" s="29">
         <f t="shared" si="0"/>
@@ -12542,7 +12542,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A149" s="22">
         <v>46108</v>
       </c>
@@ -12560,7 +12560,7 @@
         <v>15</v>
       </c>
       <c r="G149" s="28" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H149" s="29">
         <f t="shared" si="0"/>
@@ -12573,7 +12573,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A150" s="31">
         <v>46109</v>
       </c>
@@ -12592,7 +12592,7 @@
       <c r="I150" s="35"/>
       <c r="J150" s="35"/>
     </row>
-    <row r="151" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A151" s="31">
         <v>46110</v>
       </c>
@@ -12629,7 +12629,7 @@
         <v>15</v>
       </c>
       <c r="G152" s="28" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H152" s="29">
         <f t="shared" si="0"/>
@@ -12660,7 +12660,7 @@
         <v>15</v>
       </c>
       <c r="G153" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H153" s="29">
         <f t="shared" si="0"/>
@@ -12691,7 +12691,7 @@
         <v>15</v>
       </c>
       <c r="G154" s="28" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H154" s="29">
         <f t="shared" si="0"/>
@@ -12722,7 +12722,7 @@
         <v>15</v>
       </c>
       <c r="G155" s="28" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H155" s="29">
         <f t="shared" si="0"/>
@@ -12753,7 +12753,7 @@
         <v>15</v>
       </c>
       <c r="G156" s="28" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H156" s="29">
         <f t="shared" si="0"/>
@@ -12784,7 +12784,7 @@
         <v>15</v>
       </c>
       <c r="G157" s="28" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H157" s="29">
         <f t="shared" si="0"/>
@@ -12815,7 +12815,7 @@
         <v>15</v>
       </c>
       <c r="G158" s="28" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H158" s="29">
         <f t="shared" si="0"/>
@@ -12846,7 +12846,7 @@
         <v>15</v>
       </c>
       <c r="G159" s="28" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H159" s="29">
         <f t="shared" si="0"/>
@@ -12877,7 +12877,7 @@
         <v>15</v>
       </c>
       <c r="G160" s="28" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H160" s="29">
         <f t="shared" ref="H160:H165" si="1">J160-I160</f>
@@ -12908,7 +12908,7 @@
         <v>15</v>
       </c>
       <c r="G161" s="28" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H161" s="29">
         <f t="shared" si="1"/>
@@ -12939,7 +12939,7 @@
         <v>15</v>
       </c>
       <c r="G162" s="28" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H162" s="29">
         <f t="shared" si="1"/>
@@ -12970,7 +12970,7 @@
         <v>15</v>
       </c>
       <c r="G163" s="28" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H163" s="29">
         <f t="shared" si="1"/>
@@ -13001,7 +13001,7 @@
         <v>15</v>
       </c>
       <c r="G164" s="28" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H164" s="29">
         <f t="shared" si="1"/>
@@ -13032,7 +13032,7 @@
         <v>15</v>
       </c>
       <c r="G165" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H165" s="29">
         <f t="shared" si="1"/>
@@ -13057,7 +13057,7 @@
       <c r="H167" s="36"/>
       <c r="I167" s="37"/>
     </row>
-    <row r="168" spans="1:10" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="5"/>
@@ -13071,7 +13071,7 @@
       </c>
       <c r="H168" s="40"/>
     </row>
-    <row r="169" spans="1:10" ht="13.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:10" ht="13.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A169" s="4"/>
       <c r="B169" s="4"/>
       <c r="C169" s="9"/>
@@ -13084,7 +13084,7 @@
       </c>
       <c r="H169" s="40"/>
     </row>
-    <row r="170" spans="1:10" ht="13.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:10" ht="13.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A170" s="116" t="s">
         <v>23</v>
       </c>
@@ -13095,7 +13095,7 @@
       <c r="F170" s="2"/>
       <c r="H170" s="40"/>
     </row>
-    <row r="171" spans="1:10" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A171" s="13"/>
       <c r="B171" s="13"/>
       <c r="C171" s="6"/>
@@ -13109,7 +13109,7 @@
       </c>
       <c r="H171" s="38"/>
     </row>
-    <row r="172" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A172" s="117" t="s">
         <v>25</v>
       </c>
@@ -13125,7 +13125,7 @@
       </c>
       <c r="H172" s="40"/>
     </row>
-    <row r="173" spans="1:10" ht="14.45" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -13139,7 +13139,7 @@
       </c>
       <c r="H173" s="40"/>
     </row>
-    <row r="174" spans="1:10" ht="13.9" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -13148,7 +13148,7 @@
       <c r="F174" s="2"/>
       <c r="H174" s="40"/>
     </row>
-    <row r="175" spans="1:10" ht="13.9" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -13348,118 +13348,118 @@
       <c r="F7" s="86"/>
     </row>
     <row r="8" spans="1:15" ht="27.4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="123" t="s">
+      <c r="A8" s="126" t="s">
         <v>183</v>
       </c>
-      <c r="B8" s="123"/>
-      <c r="C8" s="123"/>
-      <c r="D8" s="123"/>
-      <c r="E8" s="123"/>
-      <c r="F8" s="123"/>
+      <c r="B8" s="126"/>
+      <c r="C8" s="126"/>
+      <c r="D8" s="126"/>
+      <c r="E8" s="126"/>
+      <c r="F8" s="126"/>
     </row>
     <row r="9" spans="1:15" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="83" t="s">
         <v>187</v>
       </c>
-      <c r="B9" s="120" t="s">
+      <c r="B9" s="129" t="s">
         <v>184</v>
       </c>
-      <c r="C9" s="121"/>
-      <c r="D9" s="120" t="s">
+      <c r="C9" s="130"/>
+      <c r="D9" s="129" t="s">
         <v>93</v>
       </c>
-      <c r="E9" s="121"/>
+      <c r="E9" s="130"/>
       <c r="F9" s="84" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A10" s="79"/>
-      <c r="B10" s="122" t="s">
+      <c r="B10" s="120" t="s">
         <v>185</v>
       </c>
-      <c r="C10" s="122"/>
-      <c r="D10" s="122" t="s">
+      <c r="C10" s="120"/>
+      <c r="D10" s="120" t="s">
         <v>130</v>
       </c>
-      <c r="E10" s="122"/>
+      <c r="E10" s="120"/>
       <c r="F10" s="78">
         <v>200</v>
       </c>
-      <c r="G10" s="118" t="s">
+      <c r="G10" s="127" t="s">
         <v>186</v>
       </c>
-      <c r="H10" s="119"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="119"/>
-      <c r="K10" s="119"/>
-      <c r="L10" s="119"/>
-      <c r="M10" s="119"/>
-      <c r="N10" s="119"/>
-      <c r="O10" s="119"/>
+      <c r="H10" s="128"/>
+      <c r="I10" s="128"/>
+      <c r="J10" s="128"/>
+      <c r="K10" s="128"/>
+      <c r="L10" s="128"/>
+      <c r="M10" s="128"/>
+      <c r="N10" s="128"/>
+      <c r="O10" s="128"/>
     </row>
     <row r="11" spans="1:15" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A11" s="79"/>
-      <c r="B11" s="124" t="s">
+      <c r="B11" s="118" t="s">
         <v>188</v>
       </c>
-      <c r="C11" s="125"/>
-      <c r="D11" s="122" t="s">
+      <c r="C11" s="119"/>
+      <c r="D11" s="120" t="s">
         <v>136</v>
       </c>
-      <c r="E11" s="122"/>
+      <c r="E11" s="120"/>
       <c r="F11" s="78"/>
     </row>
     <row r="12" spans="1:15" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A12" s="79"/>
-      <c r="B12" s="124" t="s">
+      <c r="B12" s="118" t="s">
         <v>189</v>
       </c>
-      <c r="C12" s="125"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="122"/>
+      <c r="C12" s="119"/>
+      <c r="D12" s="120"/>
+      <c r="E12" s="120"/>
       <c r="F12" s="78"/>
     </row>
     <row r="13" spans="1:15" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A13" s="79"/>
-      <c r="B13" s="124"/>
-      <c r="C13" s="125"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="122"/>
+      <c r="B13" s="118"/>
+      <c r="C13" s="119"/>
+      <c r="D13" s="120"/>
+      <c r="E13" s="120"/>
       <c r="F13" s="78"/>
     </row>
     <row r="14" spans="1:15" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A14" s="79"/>
-      <c r="B14" s="124"/>
-      <c r="C14" s="125"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="122"/>
+      <c r="B14" s="118"/>
+      <c r="C14" s="119"/>
+      <c r="D14" s="120"/>
+      <c r="E14" s="120"/>
       <c r="F14" s="78"/>
     </row>
     <row r="15" spans="1:15" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A15" s="79"/>
-      <c r="B15" s="129"/>
-      <c r="C15" s="130"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="122"/>
+      <c r="B15" s="124"/>
+      <c r="C15" s="125"/>
+      <c r="D15" s="120"/>
+      <c r="E15" s="120"/>
       <c r="F15" s="78"/>
     </row>
     <row r="16" spans="1:15" ht="13.15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="79"/>
-      <c r="B16" s="124"/>
-      <c r="C16" s="125"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
+      <c r="B16" s="118"/>
+      <c r="C16" s="119"/>
+      <c r="D16" s="120"/>
+      <c r="E16" s="120"/>
       <c r="F16" s="78"/>
     </row>
     <row r="17" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="126" t="s">
+      <c r="A17" s="121" t="s">
         <v>95</v>
       </c>
-      <c r="B17" s="127"/>
-      <c r="C17" s="127"/>
-      <c r="D17" s="127"/>
-      <c r="E17" s="128"/>
+      <c r="B17" s="122"/>
+      <c r="C17" s="122"/>
+      <c r="D17" s="122"/>
+      <c r="E17" s="123"/>
       <c r="F17" s="77">
         <f>SUM(F10:F16)</f>
         <v>200</v>
@@ -13475,6 +13475,16 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="G10:O10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="A17:E17"/>
@@ -13484,16 +13494,6 @@
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:E16"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="G10:O10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7 D18" xr:uid="{517DF1E8-3052-48CF-9AE1-C19E6ECB6686}">
@@ -14472,6 +14472,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AD10A028B4ACBB47B37340D8D4079B36" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="436e80374471046821afb96e56969fce">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="819cb4b524acab89028d2f2d821df341" ns2:_="">
     <xsd:import namespace="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
@@ -14609,12 +14615,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -14625,6 +14625,15 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65AD6DCD-C979-41C2-B150-658688DCE060}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4F2C86D-6131-4266-84D3-BE8E7F63755D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14642,15 +14651,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65AD6DCD-C979-41C2-B150-658688DCE060}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AC3B20F-3DA5-41E6-83ED-7E6C76D4B764}">
   <ds:schemaRefs>

--- a/SSIS-Project/Timesheets/Teolan/Teolan_Govender_March_FinalWeek.xlsx
+++ b/SSIS-Project/Timesheets/Teolan/Teolan_Govender_March_FinalWeek.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sc_TeolanGovender_2026\SSIS-Project\Timesheets\Teolan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81FB146C-B9C2-4C3F-87CF-C610041DB79C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC7A982-1AC2-49F5-9158-E9FAE5D62803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{1C8F8026-B005-4B08-94D3-371A77F74D8F}"/>
   </bookViews>
@@ -733,9 +733,6 @@
     <t>Learning</t>
   </si>
   <si>
-    <t>Started working on dream boards</t>
-  </si>
-  <si>
     <t>Continued working on dream boards</t>
   </si>
   <si>
@@ -1033,7 +1030,10 @@
     <t>Join retrospective meeting with Bongani</t>
   </si>
   <si>
-    <t>Met with Shaila, Angela and the team for first onboarding and Discovery registration meeting - update</t>
+    <t>Met with Shaila, Angela and the team for first onboarding and Discovery registration meeting</t>
+  </si>
+  <si>
+    <t>Started working on dream boards - update</t>
   </si>
 </sst>
 </file>
@@ -2126,13 +2126,28 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2148,21 +2163,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="H44" s="38"/>
     </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="117" t="s">
         <v>25</v>
       </c>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="H45" s="40"/>
     </row>
-    <row r="46" spans="1:10" ht="14.45" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="H46" s="40"/>
     </row>
-    <row r="47" spans="1:10" ht="13.9" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -4510,7 +4510,7 @@
       <c r="F47" s="2"/>
       <c r="H47" s="40"/>
     </row>
-    <row r="48" spans="1:10" ht="13.9" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -4521,7 +4521,7 @@
       <c r="F48" s="21"/>
       <c r="H48" s="40"/>
     </row>
-    <row r="49" spans="5:8" ht="13.15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="5:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E49" s="39"/>
       <c r="H49" s="40"/>
     </row>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="H43" s="38"/>
     </row>
-    <row r="44" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="117" t="s">
         <v>25</v>
       </c>
@@ -5362,7 +5362,7 @@
       </c>
       <c r="H44" s="40"/>
     </row>
-    <row r="45" spans="1:10" ht="14.45" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="H45" s="40"/>
     </row>
-    <row r="46" spans="1:10" ht="13.9" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -5385,7 +5385,7 @@
       <c r="F46" s="2"/>
       <c r="H46" s="40"/>
     </row>
-    <row r="47" spans="1:10" ht="13.9" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -5396,7 +5396,7 @@
       <c r="F47" s="21"/>
       <c r="H47" s="40"/>
     </row>
-    <row r="48" spans="1:10" ht="13.15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E48" s="39"/>
       <c r="H48" s="40"/>
     </row>
@@ -6266,7 +6266,7 @@
       <c r="F43" s="2"/>
       <c r="H43" s="40"/>
     </row>
-    <row r="44" spans="1:10" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A44" s="13"/>
       <c r="B44" s="13"/>
       <c r="C44" s="6"/>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="H44" s="38"/>
     </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="117" t="s">
         <v>25</v>
       </c>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="H45" s="40"/>
     </row>
-    <row r="46" spans="1:10" ht="14.45" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="H46" s="40"/>
     </row>
-    <row r="47" spans="1:10" ht="13.9" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -6319,7 +6319,7 @@
       <c r="F47" s="2"/>
       <c r="H47" s="40"/>
     </row>
-    <row r="48" spans="1:10" ht="13.9" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -6330,7 +6330,7 @@
       <c r="F48" s="21"/>
       <c r="H48" s="40"/>
     </row>
-    <row r="49" spans="5:8" ht="13.15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="5:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E49" s="39"/>
       <c r="H49" s="40"/>
     </row>
@@ -7178,7 +7178,7 @@
       <c r="F43" s="2"/>
       <c r="H43" s="40"/>
     </row>
-    <row r="44" spans="1:10" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A44" s="13"/>
       <c r="B44" s="13"/>
       <c r="C44" s="6"/>
@@ -7192,7 +7192,7 @@
       </c>
       <c r="H44" s="38"/>
     </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="117" t="s">
         <v>25</v>
       </c>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="H45" s="40"/>
     </row>
-    <row r="46" spans="1:10" ht="14.45" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="H46" s="40"/>
     </row>
-    <row r="47" spans="1:10" ht="13.9" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -7231,7 +7231,7 @@
       <c r="F47" s="2"/>
       <c r="H47" s="40"/>
     </row>
-    <row r="48" spans="1:10" ht="13.9" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -7242,7 +7242,7 @@
       <c r="F48" s="21"/>
       <c r="H48" s="40"/>
     </row>
-    <row r="49" spans="5:8" ht="13.15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="5:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E49" s="39"/>
       <c r="H49" s="40"/>
     </row>
@@ -8318,7 +8318,7 @@
         <v>15</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H10" s="29">
         <f t="shared" ref="H10:H159" si="0">J10-I10</f>
@@ -8331,7 +8331,7 @@
         <v>0.40277777777777779</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="12.6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A11" s="22">
         <v>46083</v>
       </c>
@@ -8349,7 +8349,7 @@
         <v>15</v>
       </c>
       <c r="G11" s="28" t="s">
-        <v>230</v>
+        <v>330</v>
       </c>
       <c r="H11" s="29">
         <f t="shared" si="0"/>
@@ -8380,7 +8380,7 @@
         <v>15</v>
       </c>
       <c r="G12" s="28" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H12" s="29">
         <f t="shared" si="0"/>
@@ -8411,7 +8411,7 @@
         <v>15</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H13" s="29">
         <f t="shared" si="0"/>
@@ -8442,7 +8442,7 @@
         <v>15</v>
       </c>
       <c r="G14" s="28" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H14" s="29">
         <f t="shared" si="0"/>
@@ -8473,7 +8473,7 @@
         <v>15</v>
       </c>
       <c r="G15" s="28" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H15" s="29">
         <f t="shared" si="0"/>
@@ -8504,7 +8504,7 @@
         <v>15</v>
       </c>
       <c r="G16" s="28" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H16" s="29">
         <f t="shared" si="0"/>
@@ -8535,7 +8535,7 @@
         <v>15</v>
       </c>
       <c r="G17" s="28" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H17" s="29">
         <f t="shared" si="0"/>
@@ -8566,7 +8566,7 @@
         <v>15</v>
       </c>
       <c r="G18" s="28" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H18" s="29">
         <f t="shared" si="0"/>
@@ -8597,7 +8597,7 @@
         <v>15</v>
       </c>
       <c r="G19" s="28" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H19" s="29">
         <f t="shared" si="0"/>
@@ -8628,7 +8628,7 @@
         <v>15</v>
       </c>
       <c r="G20" s="28" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H20" s="29">
         <f t="shared" si="0"/>
@@ -8659,7 +8659,7 @@
         <v>15</v>
       </c>
       <c r="G21" s="28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H21" s="29">
         <f t="shared" si="0"/>
@@ -8672,7 +8672,7 @@
         <v>0.64583333333333337</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A22" s="22">
         <v>46085</v>
       </c>
@@ -8690,7 +8690,7 @@
         <v>15</v>
       </c>
       <c r="G22" s="28" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H22" s="29">
         <f t="shared" si="0"/>
@@ -8703,7 +8703,7 @@
         <v>0.70833333333333337</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A23" s="22">
         <v>46086</v>
       </c>
@@ -8721,7 +8721,7 @@
         <v>15</v>
       </c>
       <c r="G23" s="28" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H23" s="29">
         <f t="shared" si="0"/>
@@ -8734,7 +8734,7 @@
         <v>0.34027777777777779</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="22">
         <v>46086</v>
       </c>
@@ -8752,7 +8752,7 @@
         <v>15</v>
       </c>
       <c r="G24" s="28" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H24" s="29">
         <f t="shared" si="0"/>
@@ -8765,7 +8765,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A25" s="22">
         <v>46086</v>
       </c>
@@ -8783,7 +8783,7 @@
         <v>15</v>
       </c>
       <c r="G25" s="28" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H25" s="29">
         <f t="shared" si="0"/>
@@ -8796,7 +8796,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="25.15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A26" s="22">
         <v>46086</v>
       </c>
@@ -8814,7 +8814,7 @@
         <v>15</v>
       </c>
       <c r="G26" s="28" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H26" s="29">
         <f t="shared" si="0"/>
@@ -8827,7 +8827,7 @@
         <v>0.72916666666666663</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="50.45" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A27" s="22">
         <v>46087</v>
       </c>
@@ -8845,7 +8845,7 @@
         <v>15</v>
       </c>
       <c r="G27" s="28" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H27" s="29">
         <f t="shared" si="0"/>
@@ -8876,7 +8876,7 @@
         <v>15</v>
       </c>
       <c r="G28" s="28" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H28" s="29">
         <f t="shared" si="0"/>
@@ -8907,7 +8907,7 @@
         <v>15</v>
       </c>
       <c r="G29" s="28" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H29" s="29">
         <f t="shared" si="0"/>
@@ -8938,7 +8938,7 @@
         <v>15</v>
       </c>
       <c r="G30" s="28" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H30" s="29">
         <f t="shared" si="0"/>
@@ -9007,7 +9007,7 @@
         <v>15</v>
       </c>
       <c r="G33" s="28" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H33" s="29">
         <f t="shared" si="0"/>
@@ -9038,7 +9038,7 @@
         <v>15</v>
       </c>
       <c r="G34" s="28" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H34" s="29">
         <f t="shared" si="0"/>
@@ -9069,7 +9069,7 @@
         <v>15</v>
       </c>
       <c r="G35" s="28" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H35" s="29">
         <f t="shared" si="0"/>
@@ -9100,7 +9100,7 @@
         <v>15</v>
       </c>
       <c r="G36" s="28" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H36" s="29">
         <f t="shared" si="0"/>
@@ -9131,7 +9131,7 @@
         <v>15</v>
       </c>
       <c r="G37" s="28" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H37" s="29">
         <f t="shared" si="0"/>
@@ -9162,7 +9162,7 @@
         <v>15</v>
       </c>
       <c r="G38" s="28" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H38" s="29">
         <f t="shared" si="0"/>
@@ -9193,7 +9193,7 @@
         <v>15</v>
       </c>
       <c r="G39" s="28" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H39" s="29">
         <f t="shared" si="0"/>
@@ -9224,7 +9224,7 @@
         <v>15</v>
       </c>
       <c r="G40" s="28" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H40" s="29">
         <f t="shared" si="0"/>
@@ -9255,7 +9255,7 @@
         <v>15</v>
       </c>
       <c r="G41" s="28" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H41" s="29">
         <f t="shared" si="0"/>
@@ -9286,7 +9286,7 @@
         <v>15</v>
       </c>
       <c r="G42" s="28" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H42" s="29">
         <f t="shared" si="0"/>
@@ -9317,7 +9317,7 @@
         <v>15</v>
       </c>
       <c r="G43" s="28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H43" s="29">
         <f t="shared" si="0"/>
@@ -9348,7 +9348,7 @@
         <v>15</v>
       </c>
       <c r="G44" s="28" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H44" s="29">
         <f t="shared" si="0"/>
@@ -9379,7 +9379,7 @@
         <v>15</v>
       </c>
       <c r="G45" s="28" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H45" s="29">
         <f t="shared" si="0"/>
@@ -9410,7 +9410,7 @@
         <v>15</v>
       </c>
       <c r="G46" s="28" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H46" s="29">
         <f t="shared" si="0"/>
@@ -9441,7 +9441,7 @@
         <v>15</v>
       </c>
       <c r="G47" s="28" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H47" s="29">
         <f t="shared" si="0"/>
@@ -9472,7 +9472,7 @@
         <v>15</v>
       </c>
       <c r="G48" s="28" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H48" s="29">
         <f t="shared" si="0"/>
@@ -9503,7 +9503,7 @@
         <v>15</v>
       </c>
       <c r="G49" s="28" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H49" s="29">
         <f t="shared" si="0"/>
@@ -9534,7 +9534,7 @@
         <v>15</v>
       </c>
       <c r="G50" s="28" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H50" s="29">
         <f t="shared" si="0"/>
@@ -9565,7 +9565,7 @@
         <v>15</v>
       </c>
       <c r="G51" s="28" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H51" s="29">
         <f t="shared" si="0"/>
@@ -9596,7 +9596,7 @@
         <v>15</v>
       </c>
       <c r="G52" s="28" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H52" s="29">
         <f t="shared" si="0"/>
@@ -9627,7 +9627,7 @@
         <v>15</v>
       </c>
       <c r="G53" s="28" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H53" s="29">
         <f t="shared" si="0"/>
@@ -9658,7 +9658,7 @@
         <v>15</v>
       </c>
       <c r="G54" s="28" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H54" s="29">
         <f t="shared" si="0"/>
@@ -9689,7 +9689,7 @@
         <v>15</v>
       </c>
       <c r="G55" s="28" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H55" s="29">
         <f t="shared" si="0"/>
@@ -9720,7 +9720,7 @@
         <v>15</v>
       </c>
       <c r="G56" s="28" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H56" s="29">
         <f t="shared" si="0"/>
@@ -9751,7 +9751,7 @@
         <v>15</v>
       </c>
       <c r="G57" s="28" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H57" s="29">
         <f t="shared" si="0"/>
@@ -9782,7 +9782,7 @@
         <v>15</v>
       </c>
       <c r="G58" s="28" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H58" s="29">
         <f t="shared" si="0"/>
@@ -9813,7 +9813,7 @@
         <v>15</v>
       </c>
       <c r="G59" s="28" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H59" s="29">
         <f t="shared" si="0"/>
@@ -9844,7 +9844,7 @@
         <v>15</v>
       </c>
       <c r="G60" s="28" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H60" s="29">
         <f t="shared" si="0"/>
@@ -9875,7 +9875,7 @@
         <v>15</v>
       </c>
       <c r="G61" s="28" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H61" s="29">
         <f t="shared" si="0"/>
@@ -9906,7 +9906,7 @@
         <v>15</v>
       </c>
       <c r="G62" s="28" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H62" s="29">
         <f t="shared" si="0"/>
@@ -9937,7 +9937,7 @@
         <v>15</v>
       </c>
       <c r="G63" s="28" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H63" s="29">
         <f t="shared" si="0"/>
@@ -9968,7 +9968,7 @@
         <v>15</v>
       </c>
       <c r="G64" s="28" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H64" s="29">
         <f t="shared" si="0"/>
@@ -9999,7 +9999,7 @@
         <v>15</v>
       </c>
       <c r="G65" s="28" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H65" s="29">
         <f t="shared" si="0"/>
@@ -10030,7 +10030,7 @@
         <v>15</v>
       </c>
       <c r="G66" s="28" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H66" s="29">
         <f t="shared" si="0"/>
@@ -10061,7 +10061,7 @@
         <v>15</v>
       </c>
       <c r="G67" s="28" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H67" s="29">
         <f t="shared" si="0"/>
@@ -10092,7 +10092,7 @@
         <v>15</v>
       </c>
       <c r="G68" s="28" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H68" s="29">
         <f t="shared" si="0"/>
@@ -10123,7 +10123,7 @@
         <v>15</v>
       </c>
       <c r="G69" s="28" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H69" s="29">
         <f t="shared" si="0"/>
@@ -10154,7 +10154,7 @@
         <v>15</v>
       </c>
       <c r="G70" s="28" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H70" s="29">
         <f t="shared" si="0"/>
@@ -10223,7 +10223,7 @@
         <v>15</v>
       </c>
       <c r="G73" s="28" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H73" s="29">
         <f t="shared" si="0"/>
@@ -10254,7 +10254,7 @@
         <v>15</v>
       </c>
       <c r="G74" s="28" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H74" s="29">
         <f t="shared" si="0"/>
@@ -10285,7 +10285,7 @@
         <v>15</v>
       </c>
       <c r="G75" s="28" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H75" s="29">
         <f t="shared" si="0"/>
@@ -10316,7 +10316,7 @@
         <v>15</v>
       </c>
       <c r="G76" s="28" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H76" s="29">
         <f t="shared" si="0"/>
@@ -10347,7 +10347,7 @@
         <v>15</v>
       </c>
       <c r="G77" s="28" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H77" s="29">
         <f t="shared" si="0"/>
@@ -10378,7 +10378,7 @@
         <v>15</v>
       </c>
       <c r="G78" s="28" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H78" s="29">
         <f t="shared" si="0"/>
@@ -10409,7 +10409,7 @@
         <v>15</v>
       </c>
       <c r="G79" s="28" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H79" s="29">
         <f t="shared" si="0"/>
@@ -10440,7 +10440,7 @@
         <v>15</v>
       </c>
       <c r="G80" s="28" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H80" s="29">
         <f t="shared" si="0"/>
@@ -10471,7 +10471,7 @@
         <v>15</v>
       </c>
       <c r="G81" s="28" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H81" s="29">
         <f t="shared" si="0"/>
@@ -10502,7 +10502,7 @@
         <v>15</v>
       </c>
       <c r="G82" s="28" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H82" s="29">
         <f t="shared" si="0"/>
@@ -10533,7 +10533,7 @@
         <v>15</v>
       </c>
       <c r="G83" s="28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H83" s="29">
         <f t="shared" si="0"/>
@@ -10564,7 +10564,7 @@
         <v>15</v>
       </c>
       <c r="G84" s="28" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H84" s="29">
         <f t="shared" si="0"/>
@@ -10595,7 +10595,7 @@
         <v>15</v>
       </c>
       <c r="G85" s="28" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H85" s="29">
         <f t="shared" si="0"/>
@@ -10626,7 +10626,7 @@
         <v>15</v>
       </c>
       <c r="G86" s="28" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H86" s="29">
         <f t="shared" si="0"/>
@@ -10657,7 +10657,7 @@
         <v>15</v>
       </c>
       <c r="G87" s="28" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H87" s="29">
         <f t="shared" si="0"/>
@@ -10688,7 +10688,7 @@
         <v>15</v>
       </c>
       <c r="G88" s="28" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H88" s="29">
         <f t="shared" si="0"/>
@@ -10719,7 +10719,7 @@
         <v>15</v>
       </c>
       <c r="G89" s="28" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H89" s="29">
         <f t="shared" si="0"/>
@@ -10750,7 +10750,7 @@
         <v>15</v>
       </c>
       <c r="G90" s="28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H90" s="29">
         <f t="shared" si="0"/>
@@ -10781,7 +10781,7 @@
         <v>15</v>
       </c>
       <c r="G91" s="28" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H91" s="29">
         <f t="shared" si="0"/>
@@ -10812,7 +10812,7 @@
         <v>15</v>
       </c>
       <c r="G92" s="28" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H92" s="29">
         <f t="shared" si="0"/>
@@ -10843,7 +10843,7 @@
         <v>15</v>
       </c>
       <c r="G93" s="28" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H93" s="29">
         <f t="shared" si="0"/>
@@ -10868,7 +10868,7 @@
         <v>15</v>
       </c>
       <c r="G94" s="28" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H94" s="29">
         <f t="shared" si="0"/>
@@ -10899,7 +10899,7 @@
         <v>15</v>
       </c>
       <c r="G95" s="28" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H95" s="29">
         <f t="shared" si="0"/>
@@ -10930,7 +10930,7 @@
         <v>15</v>
       </c>
       <c r="G96" s="28" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H96" s="29">
         <f t="shared" si="0"/>
@@ -10961,7 +10961,7 @@
         <v>15</v>
       </c>
       <c r="G97" s="28" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H97" s="29">
         <f t="shared" si="0"/>
@@ -10992,7 +10992,7 @@
         <v>15</v>
       </c>
       <c r="G98" s="28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H98" s="29">
         <f t="shared" si="0"/>
@@ -11023,7 +11023,7 @@
         <v>15</v>
       </c>
       <c r="G99" s="28" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H99" s="29">
         <f t="shared" si="0"/>
@@ -11054,7 +11054,7 @@
         <v>15</v>
       </c>
       <c r="G100" s="28" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H100" s="29">
         <f t="shared" si="0"/>
@@ -11085,7 +11085,7 @@
         <v>15</v>
       </c>
       <c r="G101" s="28" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H101" s="29">
         <f t="shared" si="0"/>
@@ -11116,7 +11116,7 @@
         <v>15</v>
       </c>
       <c r="G102" s="28" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H102" s="29">
         <f t="shared" si="0"/>
@@ -11147,7 +11147,7 @@
         <v>15</v>
       </c>
       <c r="G103" s="28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H103" s="29">
         <f t="shared" si="0"/>
@@ -11178,7 +11178,7 @@
         <v>15</v>
       </c>
       <c r="G104" s="28" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H104" s="29">
         <f t="shared" si="0"/>
@@ -11210,7 +11210,7 @@
         <v>15</v>
       </c>
       <c r="G105" s="28" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H105" s="29">
         <f t="shared" si="0"/>
@@ -11241,7 +11241,7 @@
         <v>15</v>
       </c>
       <c r="G106" s="28" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H106" s="29">
         <f t="shared" si="0"/>
@@ -11272,7 +11272,7 @@
         <v>15</v>
       </c>
       <c r="G107" s="28" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H107" s="29">
         <f>J107-I106</f>
@@ -11353,7 +11353,7 @@
         <v>15</v>
       </c>
       <c r="G110" s="28" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H110" s="29">
         <f t="shared" si="0"/>
@@ -11384,7 +11384,7 @@
         <v>15</v>
       </c>
       <c r="G111" s="28" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H111" s="29">
         <f t="shared" si="0"/>
@@ -11415,7 +11415,7 @@
         <v>15</v>
       </c>
       <c r="G112" s="28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H112" s="29">
         <f t="shared" si="0"/>
@@ -11446,7 +11446,7 @@
         <v>15</v>
       </c>
       <c r="G113" s="28" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H113" s="29">
         <f t="shared" si="0"/>
@@ -11477,7 +11477,7 @@
         <v>15</v>
       </c>
       <c r="G114" s="28" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H114" s="29">
         <f t="shared" si="0"/>
@@ -11508,7 +11508,7 @@
         <v>15</v>
       </c>
       <c r="G115" s="28" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H115" s="29">
         <f t="shared" si="0"/>
@@ -11539,7 +11539,7 @@
         <v>15</v>
       </c>
       <c r="G116" s="28" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H116" s="29">
         <f t="shared" si="0"/>
@@ -11570,7 +11570,7 @@
         <v>15</v>
       </c>
       <c r="G117" s="28" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H117" s="29">
         <f t="shared" si="0"/>
@@ -11601,7 +11601,7 @@
         <v>15</v>
       </c>
       <c r="G118" s="28" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H118" s="29">
         <f t="shared" si="0"/>
@@ -11632,7 +11632,7 @@
         <v>15</v>
       </c>
       <c r="G119" s="28" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H119" s="29">
         <f t="shared" si="0"/>
@@ -11663,7 +11663,7 @@
         <v>15</v>
       </c>
       <c r="G120" s="28" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H120" s="29">
         <f t="shared" si="0"/>
@@ -11694,7 +11694,7 @@
         <v>15</v>
       </c>
       <c r="G121" s="28" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H121" s="29">
         <f t="shared" si="0"/>
@@ -11725,7 +11725,7 @@
         <v>15</v>
       </c>
       <c r="G122" s="28" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H122" s="29">
         <f t="shared" si="0"/>
@@ -11756,7 +11756,7 @@
         <v>15</v>
       </c>
       <c r="G123" s="28" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H123" s="29">
         <f t="shared" si="0"/>
@@ -11787,7 +11787,7 @@
         <v>15</v>
       </c>
       <c r="G124" s="28" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H124" s="29">
         <f t="shared" si="0"/>
@@ -11818,7 +11818,7 @@
         <v>15</v>
       </c>
       <c r="G125" s="28" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H125" s="29">
         <f t="shared" si="0"/>
@@ -11849,7 +11849,7 @@
         <v>15</v>
       </c>
       <c r="G126" s="28" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H126" s="29">
         <f t="shared" si="0"/>
@@ -11880,7 +11880,7 @@
         <v>15</v>
       </c>
       <c r="G127" s="28" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H127" s="29">
         <f t="shared" si="0"/>
@@ -11911,7 +11911,7 @@
         <v>15</v>
       </c>
       <c r="G128" s="28" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H128" s="29">
         <f t="shared" si="0"/>
@@ -11942,7 +11942,7 @@
         <v>15</v>
       </c>
       <c r="G129" s="28" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H129" s="29">
         <f t="shared" si="0"/>
@@ -11973,7 +11973,7 @@
         <v>15</v>
       </c>
       <c r="G130" s="28" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H130" s="29">
         <f t="shared" si="0"/>
@@ -12004,7 +12004,7 @@
         <v>15</v>
       </c>
       <c r="G131" s="28" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H131" s="29">
         <f t="shared" si="0"/>
@@ -12035,7 +12035,7 @@
         <v>15</v>
       </c>
       <c r="G132" s="28" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H132" s="29">
         <f t="shared" si="0"/>
@@ -12066,7 +12066,7 @@
         <v>15</v>
       </c>
       <c r="G133" s="28" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H133" s="29">
         <f t="shared" si="0"/>
@@ -12097,7 +12097,7 @@
         <v>15</v>
       </c>
       <c r="G134" s="28" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H134" s="29">
         <f t="shared" si="0"/>
@@ -12128,7 +12128,7 @@
         <v>15</v>
       </c>
       <c r="G135" s="28" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H135" s="29">
         <f t="shared" si="0"/>
@@ -12159,7 +12159,7 @@
         <v>15</v>
       </c>
       <c r="G136" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H136" s="29">
         <f t="shared" si="0"/>
@@ -12190,7 +12190,7 @@
         <v>15</v>
       </c>
       <c r="G137" s="28" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H137" s="29">
         <f t="shared" si="0"/>
@@ -12221,7 +12221,7 @@
         <v>15</v>
       </c>
       <c r="G138" s="28" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H138" s="29">
         <f t="shared" si="0"/>
@@ -12252,7 +12252,7 @@
         <v>15</v>
       </c>
       <c r="G139" s="28" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H139" s="29">
         <f t="shared" si="0"/>
@@ -12283,7 +12283,7 @@
         <v>15</v>
       </c>
       <c r="G140" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H140" s="29">
         <f t="shared" si="0"/>
@@ -12314,7 +12314,7 @@
         <v>15</v>
       </c>
       <c r="G141" s="28" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H141" s="29">
         <f t="shared" si="0"/>
@@ -12345,7 +12345,7 @@
         <v>15</v>
       </c>
       <c r="G142" s="28" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H142" s="29">
         <f t="shared" si="0"/>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="F143" s="27"/>
       <c r="G143" s="28" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H143" s="29">
         <f t="shared" si="0"/>
@@ -12405,7 +12405,7 @@
         <v>15</v>
       </c>
       <c r="G144" s="28" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H144" s="29">
         <f t="shared" si="0"/>
@@ -12436,7 +12436,7 @@
         <v>15</v>
       </c>
       <c r="G145" s="28" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H145" s="29">
         <f t="shared" si="0"/>
@@ -12467,7 +12467,7 @@
         <v>15</v>
       </c>
       <c r="G146" s="28" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H146" s="29">
         <f t="shared" si="0"/>
@@ -12498,7 +12498,7 @@
         <v>15</v>
       </c>
       <c r="G147" s="28" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H147" s="29">
         <f t="shared" si="0"/>
@@ -12529,7 +12529,7 @@
         <v>15</v>
       </c>
       <c r="G148" s="28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H148" s="29">
         <f t="shared" si="0"/>
@@ -12560,7 +12560,7 @@
         <v>15</v>
       </c>
       <c r="G149" s="28" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H149" s="29">
         <f t="shared" si="0"/>
@@ -12629,7 +12629,7 @@
         <v>15</v>
       </c>
       <c r="G152" s="28" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H152" s="29">
         <f t="shared" si="0"/>
@@ -12660,7 +12660,7 @@
         <v>15</v>
       </c>
       <c r="G153" s="28" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H153" s="29">
         <f t="shared" si="0"/>
@@ -12691,7 +12691,7 @@
         <v>15</v>
       </c>
       <c r="G154" s="28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H154" s="29">
         <f t="shared" si="0"/>
@@ -12722,7 +12722,7 @@
         <v>15</v>
       </c>
       <c r="G155" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H155" s="29">
         <f t="shared" si="0"/>
@@ -12753,7 +12753,7 @@
         <v>15</v>
       </c>
       <c r="G156" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H156" s="29">
         <f t="shared" si="0"/>
@@ -12784,7 +12784,7 @@
         <v>15</v>
       </c>
       <c r="G157" s="28" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H157" s="29">
         <f t="shared" si="0"/>
@@ -12815,7 +12815,7 @@
         <v>15</v>
       </c>
       <c r="G158" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H158" s="29">
         <f t="shared" si="0"/>
@@ -12846,7 +12846,7 @@
         <v>15</v>
       </c>
       <c r="G159" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H159" s="29">
         <f t="shared" si="0"/>
@@ -12877,7 +12877,7 @@
         <v>15</v>
       </c>
       <c r="G160" s="28" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H160" s="29">
         <f t="shared" ref="H160:H165" si="1">J160-I160</f>
@@ -12908,7 +12908,7 @@
         <v>15</v>
       </c>
       <c r="G161" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H161" s="29">
         <f t="shared" si="1"/>
@@ -12939,7 +12939,7 @@
         <v>15</v>
       </c>
       <c r="G162" s="28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H162" s="29">
         <f t="shared" si="1"/>
@@ -12970,7 +12970,7 @@
         <v>15</v>
       </c>
       <c r="G163" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H163" s="29">
         <f t="shared" si="1"/>
@@ -13001,7 +13001,7 @@
         <v>15</v>
       </c>
       <c r="G164" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H164" s="29">
         <f t="shared" si="1"/>
@@ -13032,7 +13032,7 @@
         <v>15</v>
       </c>
       <c r="G165" s="28" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H165" s="29">
         <f t="shared" si="1"/>
@@ -13348,118 +13348,118 @@
       <c r="F7" s="86"/>
     </row>
     <row r="8" spans="1:15" ht="27.4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="126" t="s">
+      <c r="A8" s="123" t="s">
         <v>183</v>
       </c>
-      <c r="B8" s="126"/>
-      <c r="C8" s="126"/>
-      <c r="D8" s="126"/>
-      <c r="E8" s="126"/>
-      <c r="F8" s="126"/>
+      <c r="B8" s="123"/>
+      <c r="C8" s="123"/>
+      <c r="D8" s="123"/>
+      <c r="E8" s="123"/>
+      <c r="F8" s="123"/>
     </row>
     <row r="9" spans="1:15" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="83" t="s">
         <v>187</v>
       </c>
-      <c r="B9" s="129" t="s">
+      <c r="B9" s="120" t="s">
         <v>184</v>
       </c>
-      <c r="C9" s="130"/>
-      <c r="D9" s="129" t="s">
+      <c r="C9" s="121"/>
+      <c r="D9" s="120" t="s">
         <v>93</v>
       </c>
-      <c r="E9" s="130"/>
+      <c r="E9" s="121"/>
       <c r="F9" s="84" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A10" s="79"/>
-      <c r="B10" s="120" t="s">
+      <c r="B10" s="122" t="s">
         <v>185</v>
       </c>
-      <c r="C10" s="120"/>
-      <c r="D10" s="120" t="s">
+      <c r="C10" s="122"/>
+      <c r="D10" s="122" t="s">
         <v>130</v>
       </c>
-      <c r="E10" s="120"/>
+      <c r="E10" s="122"/>
       <c r="F10" s="78">
         <v>200</v>
       </c>
-      <c r="G10" s="127" t="s">
+      <c r="G10" s="118" t="s">
         <v>186</v>
       </c>
-      <c r="H10" s="128"/>
-      <c r="I10" s="128"/>
-      <c r="J10" s="128"/>
-      <c r="K10" s="128"/>
-      <c r="L10" s="128"/>
-      <c r="M10" s="128"/>
-      <c r="N10" s="128"/>
-      <c r="O10" s="128"/>
+      <c r="H10" s="119"/>
+      <c r="I10" s="119"/>
+      <c r="J10" s="119"/>
+      <c r="K10" s="119"/>
+      <c r="L10" s="119"/>
+      <c r="M10" s="119"/>
+      <c r="N10" s="119"/>
+      <c r="O10" s="119"/>
     </row>
     <row r="11" spans="1:15" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A11" s="79"/>
-      <c r="B11" s="118" t="s">
+      <c r="B11" s="124" t="s">
         <v>188</v>
       </c>
-      <c r="C11" s="119"/>
-      <c r="D11" s="120" t="s">
+      <c r="C11" s="125"/>
+      <c r="D11" s="122" t="s">
         <v>136</v>
       </c>
-      <c r="E11" s="120"/>
+      <c r="E11" s="122"/>
       <c r="F11" s="78"/>
     </row>
     <row r="12" spans="1:15" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A12" s="79"/>
-      <c r="B12" s="118" t="s">
+      <c r="B12" s="124" t="s">
         <v>189</v>
       </c>
-      <c r="C12" s="119"/>
-      <c r="D12" s="120"/>
-      <c r="E12" s="120"/>
+      <c r="C12" s="125"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="122"/>
       <c r="F12" s="78"/>
     </row>
     <row r="13" spans="1:15" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A13" s="79"/>
-      <c r="B13" s="118"/>
-      <c r="C13" s="119"/>
-      <c r="D13" s="120"/>
-      <c r="E13" s="120"/>
+      <c r="B13" s="124"/>
+      <c r="C13" s="125"/>
+      <c r="D13" s="122"/>
+      <c r="E13" s="122"/>
       <c r="F13" s="78"/>
     </row>
     <row r="14" spans="1:15" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A14" s="79"/>
-      <c r="B14" s="118"/>
-      <c r="C14" s="119"/>
-      <c r="D14" s="120"/>
-      <c r="E14" s="120"/>
+      <c r="B14" s="124"/>
+      <c r="C14" s="125"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
       <c r="F14" s="78"/>
     </row>
     <row r="15" spans="1:15" ht="12.6" x14ac:dyDescent="0.2">
       <c r="A15" s="79"/>
-      <c r="B15" s="124"/>
-      <c r="C15" s="125"/>
-      <c r="D15" s="120"/>
-      <c r="E15" s="120"/>
+      <c r="B15" s="129"/>
+      <c r="C15" s="130"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="122"/>
       <c r="F15" s="78"/>
     </row>
     <row r="16" spans="1:15" ht="13.15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="79"/>
-      <c r="B16" s="118"/>
-      <c r="C16" s="119"/>
-      <c r="D16" s="120"/>
-      <c r="E16" s="120"/>
+      <c r="B16" s="124"/>
+      <c r="C16" s="125"/>
+      <c r="D16" s="122"/>
+      <c r="E16" s="122"/>
       <c r="F16" s="78"/>
     </row>
     <row r="17" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="121" t="s">
+      <c r="A17" s="126" t="s">
         <v>95</v>
       </c>
-      <c r="B17" s="122"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="122"/>
-      <c r="E17" s="123"/>
+      <c r="B17" s="127"/>
+      <c r="C17" s="127"/>
+      <c r="D17" s="127"/>
+      <c r="E17" s="128"/>
       <c r="F17" s="77">
         <f>SUM(F10:F16)</f>
         <v>200</v>
@@ -13475,16 +13475,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="G10:O10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="A17:E17"/>
@@ -13494,6 +13484,16 @@
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="G10:O10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D7 D18" xr:uid="{517DF1E8-3052-48CF-9AE1-C19E6ECB6686}">
@@ -14478,6 +14478,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AD10A028B4ACBB47B37340D8D4079B36" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="436e80374471046821afb96e56969fce">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="819cb4b524acab89028d2f2d821df341" ns2:_="">
     <xsd:import namespace="606bf0c3-7c02-4ad1-9a2b-bad21eeec9a2"/>
@@ -14615,15 +14624,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65AD6DCD-C979-41C2-B150-658688DCE060}">
   <ds:schemaRefs>
@@ -14634,6 +14634,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AC3B20F-3DA5-41E6-83ED-7E6C76D4B764}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4F2C86D-6131-4266-84D3-BE8E7F63755D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14651,14 +14659,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AC3B20F-3DA5-41E6-83ED-7E6C76D4B764}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{5138fff4-6130-46cf-adb5-ec5d984d54d5}" enabled="1" method="Privileged" siteId="{174c7352-9c5c-4558-b848-be140b444e7d}" removed="0"/>
